--- a/dashboard-ui/src/components/AggregateResults/Variable Definitions/PH2_April_Variables.xlsx
+++ b/dashboard-ui/src/components/AggregateResults/Variable Definitions/PH2_April_Variables.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="125">
   <si>
     <t>Participant ID</t>
   </si>
@@ -46,6 +46,15 @@
     <t>AF_attribute</t>
   </si>
   <si>
+    <t>AF_OtherSub_intercept</t>
+  </si>
+  <si>
+    <t>AF_OtherSub_medical</t>
+  </si>
+  <si>
+    <t>AF_OtherSub_attribute</t>
+  </si>
+  <si>
     <t>MF_intercept</t>
   </si>
   <si>
@@ -55,6 +64,15 @@
     <t>MF_attribute</t>
   </si>
   <si>
+    <t>MF_OtherSub_intercept</t>
+  </si>
+  <si>
+    <t>MF_OtherSub_medical</t>
+  </si>
+  <si>
+    <t>MF_OtherSub_attribute</t>
+  </si>
+  <si>
     <t>PS_intercept</t>
   </si>
   <si>
@@ -64,6 +82,15 @@
     <t>PS_attribute</t>
   </si>
   <si>
+    <t>PS_OtherSub_intercept</t>
+  </si>
+  <si>
+    <t>PS_OtherSub_medical</t>
+  </si>
+  <si>
+    <t>PS_OtherSub_attribute</t>
+  </si>
+  <si>
     <t>SS_intercept</t>
   </si>
   <si>
@@ -73,6 +100,15 @@
     <t>SS_attribute</t>
   </si>
   <si>
+    <t>SS_OtherSub_intercept</t>
+  </si>
+  <si>
+    <t>SS_OtherSub_medical</t>
+  </si>
+  <si>
+    <t>SS_OtherSub_attribute</t>
+  </si>
+  <si>
     <t>Active-DecisionMaking</t>
   </si>
   <si>
@@ -187,6 +223,15 @@
     <t>Affiliation Focus KDMA measurement from text-based assessment; attribute term (3 of 3 terms in regression approach)</t>
   </si>
   <si>
+    <t>Affiliation Focus KDMA measurement from text-based assessment, scored using the opposite subpopulation group of the participant; intercept term (1 of 3 terms in regression approach)</t>
+  </si>
+  <si>
+    <t>Affiliation Focus KDMA measurement from text-based assessment, scored using the opposite subpopulation group of the participant; medical urgency term (2 of 3 terms in regression approach)</t>
+  </si>
+  <si>
+    <t>Affiliation Focus KDMA measurement from text-based assessment, scored using the opposite subpopulation group of the participant; attribute term (3 of 3 terms in regression approach)</t>
+  </si>
+  <si>
     <t>Merit Focus KDMA measurement from text-based assessment; intercept term (1 of 3 terms in regression approach)</t>
   </si>
   <si>
@@ -196,6 +241,15 @@
     <t>Merit Focus KDMA measurement from text-based assessment; attribute term (3 of 3 terms in regression approach)</t>
   </si>
   <si>
+    <t>Merit Focus KDMA measurement from text-based assessment, scored using the opposite subpopulation group of the participant; intercept term (1 of 3 terms in regression approach)</t>
+  </si>
+  <si>
+    <t>Merit Focus KDMA measurement from text-based assessment, scored using the opposite subpopulation group of the participant; medical urgency term (2 of 3 terms in regression approach)</t>
+  </si>
+  <si>
+    <t>Merit Focus KDMA measurement from text-based assessment, scored using the opposite subpopulation group of the participant; attribute term (3 of 3 terms in regression approach)</t>
+  </si>
+  <si>
     <t>Personal Safety Focus KDMA measurement from text-based assessment; intercept term (1 of 3 terms in regression approach)</t>
   </si>
   <si>
@@ -205,6 +259,15 @@
     <t>Personal Safety Focus KDMA measurement from text-based assessment; attribute term (3 of 3 terms in regression approach)</t>
   </si>
   <si>
+    <t>Personal Safety Focus KDMA measurement from text-based assessment, scored using the opposite subpopulation group of the participant; intercept term (1 of 3 terms in regression approach)</t>
+  </si>
+  <si>
+    <t>Personal Safety Focus KDMA measurement from text-based assessment, scored using the opposite subpopulation group of the participant; medical urgency term (2 of 3 terms in regression approach)</t>
+  </si>
+  <si>
+    <t>Personal Safety Focus KDMA measurement from text-based assessment, scored using the opposite subpopulation group of the participant; attribute term (3 of 3 terms in regression approach)</t>
+  </si>
+  <si>
     <t>Search Focus KDMA measurement from text-based assessment; intercept term (1 of 3 terms in regression approach)</t>
   </si>
   <si>
@@ -212,6 +275,15 @@
   </si>
   <si>
     <t>Search Focus KDMA measurement from text-based assessment; attribute term (3 of 3 terms in regression approach)</t>
+  </si>
+  <si>
+    <t>Search Focus KDMA measurement from text-based assessment, scored using the opposite subpopulation group of the participant; intercept term (1 of 3 terms in regression approach)</t>
+  </si>
+  <si>
+    <t>Search Focus KDMA measurement from text-based assessment, scored using the opposite subpopulation group of the participant; medical urgency term (2 of 3 terms in regression approach)</t>
+  </si>
+  <si>
+    <t>Search Focus KDMA measurement from text-based assessment, scored using the opposite subpopulation group of the participant; attribute term (3 of 3 terms in regression approach)</t>
   </si>
   <si>
     <t>As I was reading through the scenarios and Medic decisions, I actively thought about how I would handle the same situation</t>
@@ -383,7 +455,7 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -687,7 +759,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AO6"/>
+  <dimension ref="A1:BA6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="3" width="13.862142857142858" customWidth="1" bestFit="1"/>
@@ -701,18 +773,18 @@
     <col min="9" max="9" style="3" width="110.57642857142856" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="3" width="73.005" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="3" width="87.7192857142857" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="3" width="73.005" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="3" width="110.57642857142856" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="3" width="73.005" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="3" width="38.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="3" width="34.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="3" width="87.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="3" width="73.005" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="3" width="73.005" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="3" width="32.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="3" width="32.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="3" width="32.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="3" width="32.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="3" width="38.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="3" width="34.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="3" width="73.005" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="3" width="32.57642857142857" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="3" width="32.29071428571429" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="3" width="32.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="3" width="35.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="3" width="32.29071428571429" customWidth="1" bestFit="1"/>
     <col min="24" max="24" style="3" width="35.57642857142857" customWidth="1" bestFit="1"/>
     <col min="25" max="25" style="3" width="35.57642857142857" customWidth="1" bestFit="1"/>
     <col min="26" max="26" style="3" width="35.57642857142857" customWidth="1" bestFit="1"/>
@@ -731,9 +803,21 @@
     <col min="39" max="39" style="3" width="35.57642857142857" customWidth="1" bestFit="1"/>
     <col min="40" max="40" style="3" width="35.57642857142857" customWidth="1" bestFit="1"/>
     <col min="41" max="41" style="3" width="35.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="42" max="42" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="43" max="43" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="44" max="44" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="45" max="45" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="46" max="46" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="47" max="47" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="48" max="48" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="49" max="49" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="50" max="50" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="51" max="51" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="52" max="52" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="53" max="53" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="33" customFormat="1" s="1">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -855,281 +939,389 @@
       <c r="AO1" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="AP1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AW1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AZ1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BA1" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="33" customFormat="1" s="1">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AT2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AW2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AY2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="60" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="127.5" customFormat="1" s="1">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AJ3" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AK3" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AO3" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AT3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="100.5" customFormat="1" s="1">
       <c r="A4" s="2" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -1164,24 +1356,36 @@
       <c r="AM4" s="2"/>
       <c r="AN4" s="2"/>
       <c r="AO4" s="2"/>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="2"/>
+      <c r="AS4" s="2"/>
+      <c r="AT4" s="2"/>
+      <c r="AU4" s="2"/>
+      <c r="AV4" s="2"/>
+      <c r="AW4" s="2"/>
+      <c r="AX4" s="2"/>
+      <c r="AY4" s="2"/>
+      <c r="AZ4" s="2"/>
+      <c r="BA4" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="60" customFormat="1" s="1">
       <c r="A5" s="2" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -1217,130 +1421,178 @@
       <c r="AM5" s="2"/>
       <c r="AN5" s="2"/>
       <c r="AO5" s="2"/>
+      <c r="AP5" s="2"/>
+      <c r="AQ5" s="2"/>
+      <c r="AR5" s="2"/>
+      <c r="AS5" s="2"/>
+      <c r="AT5" s="2"/>
+      <c r="AU5" s="2"/>
+      <c r="AV5" s="2"/>
+      <c r="AW5" s="2"/>
+      <c r="AX5" s="2"/>
+      <c r="AY5" s="2"/>
+      <c r="AZ5" s="2"/>
+      <c r="BA5" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="33.75" customFormat="1" s="1">
       <c r="A6" s="2" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="AD6" s="2" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="AG6" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AJ6" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AK6" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AL6" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AM6" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AN6" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AO6" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
+      </c>
+      <c r="AP6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AQ6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AR6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AS6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AT6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AU6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AV6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AW6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AX6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AY6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AZ6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA6" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
